--- a/request_forms/046_smart_access_card_replacement_request--request_forms.xlsx
+++ b/request_forms/046_smart_access_card_replacement_request--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,58 +566,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>reason_for_replacement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Reason for Replacement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>reason_for_replacement</t>
+          <t>confirm_replacement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reason_for_replacement</t>
+          <t>Has the Card Replacement Been Confirmed?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>confirm_replacement</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>confirm_replacement</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>confirmed_by</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>confirmed_by</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confirmed_date</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>confirmed_date</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>confirmed_by</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Confirmed By</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,182 +699,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>confirmed_by_title</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Confirmed By Title</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>confirmed_by_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Confirmed By Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>confirmed_by_name</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>confirmed_by</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>confirmed_by_title</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>confirmed_by_title</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>confirmed_by_department</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>confirmed_by</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>confirmed_by_location</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>confirmed_by</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>confirmed_by_phone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>confirmed_by</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -891,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -941,46 +803,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>confirmed_by_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>confirmed_by_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>access</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Access</t>
         </is>
       </c>
     </row>
@@ -992,29 +854,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1026,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1043,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1060,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1077,80 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>confirmed_by_department_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>confirmed_by_department_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>confirmed_by_location_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>confirmed_by_location_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
